--- a/artfynd/A 11855-2025 artfynd.xlsx
+++ b/artfynd/A 11855-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129851538</v>
       </c>
       <c r="B2" t="n">
-        <v>79113</v>
+        <v>79116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11855-2025 artfynd.xlsx
+++ b/artfynd/A 11855-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129851538</v>
       </c>
       <c r="B2" t="n">
-        <v>79116</v>
+        <v>79119</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11855-2025 artfynd.xlsx
+++ b/artfynd/A 11855-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129851538</v>
       </c>
       <c r="B2" t="n">
-        <v>79119</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11855-2025 artfynd.xlsx
+++ b/artfynd/A 11855-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129851538</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>79121</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11855-2025 artfynd.xlsx
+++ b/artfynd/A 11855-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129851538</v>
       </c>
       <c r="B2" t="n">
-        <v>79127</v>
+        <v>79212</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11855-2025 artfynd.xlsx
+++ b/artfynd/A 11855-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129851538</v>
       </c>
       <c r="B2" t="n">
-        <v>79212</v>
+        <v>79127</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
